--- a/src/test/output_test/Over_rate_regions/Region_over_0_100_2.5/Stats_over_0_100_2.5.xlsx
+++ b/src/test/output_test/Over_rate_regions/Region_over_0_100_2.5/Stats_over_0_100_2.5.xlsx
@@ -522,58 +522,58 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>0.97699999809265</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0.97699999809265</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>38343</v>
+        <v>37366</v>
       </c>
       <c r="G2">
-        <v>109798.5159122913</v>
+        <v>112098</v>
       </c>
       <c r="H2">
-        <v>109.7985159122913</v>
+        <v>112.098</v>
       </c>
       <c r="I2">
-        <v>-1000</v>
+        <v>-997</v>
       </c>
       <c r="J2">
-        <v>759</v>
+        <v>746</v>
       </c>
       <c r="K2">
-        <v>-253.6756122369142</v>
+        <v>-261.812878017449</v>
       </c>
       <c r="L2">
         <v>101</v>
       </c>
       <c r="M2">
-        <v>393</v>
+        <v>343</v>
       </c>
       <c r="N2">
-        <v>-186</v>
+        <v>-202.5</v>
       </c>
       <c r="O2">
-        <v>321.0054472702766</v>
+        <v>318.919705840356</v>
       </c>
       <c r="P2">
-        <v>-0.4023620761152956</v>
+        <v>-0.3687540055981197</v>
       </c>
       <c r="Q2">
-        <v>-1.109036256315855</v>
+        <v>-1.124012436315552</v>
       </c>
       <c r="R2">
-        <v>-746</v>
+        <v>-748</v>
       </c>
       <c r="S2">
-        <v>-525</v>
+        <v>-532</v>
       </c>
       <c r="T2">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="U2">
         <v>119</v>
